--- a/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
+++ b/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -588,25 +588,25 @@
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="8" t="n">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Yemlik depo motor grubu (170 kg yem deposu, milli yemlik motoru, yemlik hat sonu, elektrik kutusu ile)</t>
+          <t>Yemleme sistemi (HZC-FD-01) — 3 hat, 243 m hat uzunluğu, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10">
@@ -614,25 +614,25 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="33" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>2</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Spiral yemleme sistemi (yemlik boru, yemlik tabağı, yay, boru kelepçesi)</t>
+          <t>Kümes kontrol panosu (HZC-COM-004) — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>234</v>
+        <v>1</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>468</v>
+        <v>2</v>
       </c>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10">
@@ -640,25 +640,25 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="33" customHeight="1">
       <c r="A12" s="8" t="n">
         <v>3</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>15'li nipel sulama sistemi (20 cm'de bir krom nipelli boru, nipel çanağı, muf ve muf teli ile)</t>
+          <t>Tünel havalandırma fanı (HZC-WNT-012) — 4 adet, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>312</v>
+        <v>1</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10">
@@ -666,25 +666,25 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1">
+    <row r="13" ht="33" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>4</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Regülatör takımı</t>
+          <t>Sulama sistemi (HZC-WTR-005) — 4 hat, hat başına 312 m, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10">
@@ -692,25 +692,25 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="8" t="n">
         <v>5</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Yemlik ve suluk kaldırma sistemi (6 ve 5 mm halat, sarı ve beyaz ip, klemens, plastik makara, askı saçı, bilyalı makara)</t>
+          <t>Soğutma pedi sistemi (HZC-WNT-024) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, 2 x 15 m uzunluk (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>630</v>
+        <v>1</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1260</v>
+        <v>2</v>
       </c>
       <c r="F14" s="10" t="n"/>
       <c r="G14" s="10">
@@ -724,12 +724,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Yemlik motorlu kaldırma sistemi (1,1 kW çift redüktörlü frenli kaldırma motoru, mafsal 50'lik boru, UCP bilya, kontrol panosu dâhil)</t>
+          <t>Klape sistemi (HZC-WNT-001) — 40 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h, 2 aktüatörlü açma-kapama, 161 m hat</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Nipel motorlu kaldırma sistemi (0,75 kW çift redüktörlü frenli kaldırma motoru, mafsal 50'lik boru, UCP bilya, kontrol panosu dâhil)</t>
+          <t>Yem silosu ve nakil sistemi (HZC-SLO-004) — En az 17,77 ton galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -772,23 +772,23 @@
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>140 x 140 cm tünel havalandırma fanı</t>
+          <t>Montaj ve nakliye (—) — Kümes montajı ve nakliye bedelleri</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10">
@@ -796,51 +796,38 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>3 makaralı klape (hava giriş kapağı)</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B — KÜMES ISITMA SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="33" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Merkezi sistem katı yakıtlı sıcak hava üreteci (kazan) — kümes başına en az 290 kW (≈ 249.000 kcal/h) ısıtma kapasitesi; kümes içi branda ve hava kanalı ekipmanları, montaj ve devreye alma dâhil</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10">
-        <f>IF(F18="","",E18*F18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Klape açma sistemi</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
       <c r="D19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>4</v>
       </c>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10">
@@ -848,166 +835,72 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>7 inç dokunmatik ekran kümes kontrol panosu (uzaktan erişim, karbondioksit, nem ve basınç sensörü, 5 ısı sensörü dâhil)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10">
-        <f>IF(F20="","",E20*F20)</f>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>TOPLAM (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="13">
+        <f>SUM(G10:G19)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>15 m x 1,5 m x 15 cm PVC çerçeveli, kendinden depolu ve su pompalı tüp ped (serinletme) sistemi</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10">
-        <f>IF(F21="","",E21*F21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Ped kapağı açma sistemi</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10">
-        <f>IF(F22="","",E22*F22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>110 x 150 cm ped kapağı</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10">
-        <f>IF(F23="","",E23*F23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>18 ton galvaniz yem silosu ve alt grubu</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10">
-        <f>IF(F24="","",E24*F24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>İşçilik ve nakliye</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>tk</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10">
-        <f>IF(F25="","",E25*F25)</f>
-        <v/>
-      </c>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>TEDARİKÇİ BİLGİLERİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Tedarikçinin ticari unvanı</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Adresi</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Vergi dairesi ve numarası</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>B — KÜMES ISITMA SİSTEMİ</t>
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Telefon / e-posta</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
@@ -1017,59 +910,43 @@
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
     </row>
-    <row r="27" ht="33" customHeight="1">
-      <c r="A27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Merkezi sistem katı yakıtlı sıcak hava üreteci (kazan) — kümes başına en az 290 kW (≈ 249.000 kcal/h) ısıtma kapasitesi; kümes içi branda ve hava kanalı ekipmanları, montaj ve devreye alma dâhil</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10">
-        <f>IF(F27="","",E27*F27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="13">
-        <f>SUM(G10:G27)</f>
-        <v/>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Proforma numarası ve tarihi</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>TESLİM VE ÖDEME ŞARTLARI</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>TEDARİKÇİ BİLGİLERİ</t>
-        </is>
-      </c>
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Para birimi</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Tedarikçinin ticari unvanı</t>
+          <t>Fiyatlara KDV dâhil mi</t>
         </is>
       </c>
       <c r="B31" s="7" t="n"/>
@@ -1082,7 +959,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Adresi</t>
+          <t>Teslim yeri</t>
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
@@ -1095,7 +972,7 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Vergi dairesi ve numarası</t>
+          <t>Teslim süresi</t>
         </is>
       </c>
       <c r="B33" s="7" t="n"/>
@@ -1108,7 +985,7 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Telefon / e-posta</t>
+          <t>Ödeme şekli</t>
         </is>
       </c>
       <c r="B34" s="7" t="n"/>
@@ -1121,7 +998,7 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Proforma numarası ve tarihi</t>
+          <t>Fiyat geçerlilik süresi</t>
         </is>
       </c>
       <c r="B35" s="7" t="n"/>
@@ -1132,92 +1009,7 @@
       <c r="G35" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>TESLİM VE ÖDEME ŞARTLARI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Para birimi</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Fiyatlara KDV dâhil mi</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>Teslim yeri</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Teslim süresi</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Ödeme şekli</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Fiyat geçerlilik süresi</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Proforma, tedarikçinin kendi antetli kâğıdında, kaşe ve imzasıyla düzenlenmelidir.</t>
         </is>
@@ -1226,25 +1018,25 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="B34:G34"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B30:G30"/>
     <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="B41:G41"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B35:G35"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B25:G25"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="B31:G31"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B27:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
+++ b/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
@@ -718,13 +718,13 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="44" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>6</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Klape sistemi (HZC-WNT-001) — 40 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h, 2 aktüatörlü açma-kapama, 161 m hat</t>
+          <t>Klape sistemi (HZC-WNT-001) — 30 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h (30 x 1.750 = 52.500 m³/h, mekanik projedeki 46.717 m³/h ihtiyacının üzerinde), 2 aktüatörlü açma-kapama, 161 m hat</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">

--- a/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
+++ b/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Yemleme sistemi (HZC-FD-01) — 3 hat, 243 m hat uzunluğu, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
+          <t>Otomatik spiral yemlik sistemi (depo motor grubu ve kaldırma dâhil) (HZC-FD-01) — 3 hat, 243 m yemlik hattı, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -614,13 +614,13 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1">
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>2</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Kümes kontrol panosu (HZC-COM-004) — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+          <t>Otomatik nipel suluk sistemi (regülatör, hat sonu ve kaldırma dâhil) (HZC-WTR-005) — Kümes başına 4 hat, toplam 312 m hat, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 4 hat sonu, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Tünel havalandırma fanı (HZC-WNT-012) — 4 adet, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
+          <t>Havalandırma fanları (HZC-WNT-012) — Kümes başına 4 adet tünel fanı, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -666,13 +666,13 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>4</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Sulama sistemi (HZC-WTR-005) — 4 hat, hat başına 312 m, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
+          <t>Soğutma petek sistemi (açma-kapama ve petek panelleri dâhil) (HZC-WNT-024) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, kümes başına 2 x 15 m (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -692,13 +692,13 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
+    <row r="14" ht="33" customHeight="1">
       <c r="A14" s="8" t="n">
         <v>5</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Soğutma pedi sistemi (HZC-WNT-024) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, 2 x 15 m uzunluk (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
+          <t>Hava klape sistemi (açma-kapama hattı dâhil) (HZC-WNT-001) — Kümes başına 30 adet 26 x 56 cm izolasyonlu plastik klape, 2 aktüatörlü açma-kapama, 161 m hat</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -718,13 +718,13 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
+    <row r="15" ht="33" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>6</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Klape sistemi (HZC-WNT-001) — 30 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h (30 x 1.750 = 52.500 m³/h, mekanik projedeki 46.717 m³/h ihtiyacının üzerinde), 2 aktüatörlü açma-kapama, 161 m hat</t>
+          <t>17,67 ton silo ve aktarma grubu (HZC-SLO-004) — Kümes başına 1 adet galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -744,13 +744,13 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="8" t="n">
         <v>7</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Yem silosu ve nakil sistemi (HZC-SLO-004) — En az 17,77 ton galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
+          <t>Aydınlatma sistemi (HZC-LGHT-01) — Kümes başına 56 adet E27 / LED lamba (7-12 W), contalı duy, 266 m kablo</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -770,13 +770,13 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="14" customHeight="1">
+    <row r="17" ht="33" customHeight="1">
       <c r="A17" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Montaj ve nakliye (—) — Kümes montajı ve nakliye bedelleri</t>
+          <t>Isıtma sistemi — 350.000 kcal/h (HZC-HEA-004) — Kümes başına 1 adet; en az 1.700 m² ısıtma alanı, 350.000 kcal/h, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan, 10 mm cehennemlik</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -796,31 +796,44 @@
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B — KÜMES ISITMA SİSTEMİ</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="33" customHeight="1">
+    <row r="18" ht="33" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Kümes otomasyonu ve bilgisayar sistemi (HZC-COM-004) — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10">
+        <f>IF(F18="","",E18*F18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1">
       <c r="A19" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Merkezi sistem katı yakıtlı sıcak hava üreteci (kazan) — kümes başına en az 290 kW (≈ 249.000 kcal/h) ısıtma kapasitesi; kümes içi branda ve hava kanalı ekipmanları, montaj ve devreye alma dâhil</t>
+          <t>İşçilik ve nakliye (—) — Kümes montajı ve nakliye bedelleri</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
@@ -836,58 +849,71 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B — KÜMES ISITMA SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="33" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Merkezi sistem katı yakıtlı sıcak hava üreteci (kazan) — kümes başına en az 307 kW (≈ 264.000 kcal/h) ısıtma kapasitesi; kümes içi branda ve hava kanalı ekipmanları, montaj ve devreye alma dâhil</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10">
+        <f>IF(F21="","",E21*F21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="13">
-        <f>SUM(G10:G19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="13">
+        <f>SUM(G10:G21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>TEDARİKÇİ BİLGİLERİ</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Tedarikçinin ticari unvanı</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Adresi</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Vergi dairesi ve numarası</t>
+          <t>Tedarikçinin ticari unvanı</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +926,7 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Telefon / e-posta</t>
+          <t>Adresi</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
@@ -913,7 +939,7 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Proforma numarası ve tarihi</t>
+          <t>Vergi dairesi ve numarası</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -923,43 +949,43 @@
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Telefon / e-posta</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Proforma numarası ve tarihi</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>TESLİM VE ÖDEME ŞARTLARI</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Para birimi</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Fiyatlara KDV dâhil mi</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Teslim yeri</t>
+          <t>Para birimi</t>
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
@@ -972,7 +998,7 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Teslim süresi</t>
+          <t>Fiyatlara KDV dâhil mi</t>
         </is>
       </c>
       <c r="B33" s="7" t="n"/>
@@ -985,7 +1011,7 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Ödeme şekli</t>
+          <t>Teslim yeri</t>
         </is>
       </c>
       <c r="B34" s="7" t="n"/>
@@ -998,7 +1024,7 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Fiyat geçerlilik süresi</t>
+          <t>Teslim süresi</t>
         </is>
       </c>
       <c r="B35" s="7" t="n"/>
@@ -1008,8 +1034,34 @@
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Ödeme şekli</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+    </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Fiyat geçerlilik süresi</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Proforma, tedarikçinin kendi antetli kâğıdında, kaşe ve imzasıyla düzenlenmelidir.</t>
         </is>
@@ -1018,24 +1070,24 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="B29:G29"/>
     <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B28:G28"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B36:G36"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B35:G35"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="B31:G31"/>
     <mergeCell ref="B27:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
+++ b/belgeler/37_EKIPMAN_PROFORMA_ISTEK_LISTESI.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -672,7 +672,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Soğutma petek sistemi (açma-kapama ve petek panelleri dâhil) (HZC-WNT-024) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, kümes başına 2 x 15 m (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
+          <t>Soğutma petekleri ve kapatma sistemi (HZC-WNT-024) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, kümes başına 2 x 15 m (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>17,67 ton silo ve aktarma grubu (HZC-SLO-004) — Kümes başına 1 adet galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
+          <t>Silo ve aktarma sistemi — 17,67 ton (HZC-SLO-004) — Kümes başına 1 adet galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -744,13 +744,13 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="8" t="n">
         <v>7</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Aydınlatma sistemi (HZC-LGHT-01) — Kümes başına 56 adet E27 / LED lamba (7-12 W), contalı duy, 266 m kablo</t>
+          <t>Isıtma sistemi — 350.000 kcal/h (HZC-HEA-004) — Kümes başına 1 adet katı yakıtlı ısıtma kazanı, brandalı model, 171 m hava kanalı; en az 1.700 m² ısıtma alanı, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -770,13 +770,13 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="33" customHeight="1">
+    <row r="17" ht="44" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>8</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Isıtma sistemi — 350.000 kcal/h (HZC-HEA-004) — Kümes başına 1 adet; en az 1.700 m² ısıtma alanı, 350.000 kcal/h, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan, 10 mm cehennemlik</t>
+          <t>Kümes otomasyonu ve bilgisayar sistemi (HZC-COM-004) — HZC-70 işlemcili pano; 5 ısı, 1 nem, 1 basınç sensörü, ek alarm sensörü, sensör kablolamaları, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -796,13 +796,13 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="8" t="n">
         <v>9</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Kümes otomasyonu ve bilgisayar sistemi (HZC-COM-004) — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+          <t>İşçilik ve nakliye (—) — Kümes montajı ve nakliye bedelleri</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -822,98 +822,85 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>İşçilik ve nakliye (—) — Kümes montajı ve nakliye bedelleri</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10" t="n">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>B — KÜMES ISITMA SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="33" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Merkezi sistem katı yakıtlı sıcak hava üreteci (kazan) — kümes başına en az 307 kW (≈ 264.000 kcal/h) ısıtma kapasitesi; kümes içi branda ve hava kanalı ekipmanları, montaj ve devreye alma dâhil</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10">
-        <f>IF(F19="","",E19*F19)</f>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10">
+        <f>IF(F20="","",E20*F20)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>B — KÜMES ISITMA SİSTEMİ</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="33" customHeight="1">
-      <c r="A21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Merkezi sistem katı yakıtlı sıcak hava üreteci (kazan) — kümes başına en az 307 kW (≈ 264.000 kcal/h) ısıtma kapasitesi; kümes içi branda ve hava kanalı ekipmanları, montaj ve devreye alma dâhil</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10">
-        <f>IF(F21="","",E21*F21)</f>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>TOPLAM (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="13">
+        <f>SUM(G10:G20)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="13">
-        <f>SUM(G10:G21)</f>
-        <v/>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>TEDARİKÇİ BİLGİLERİ</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>TEDARİKÇİ BİLGİLERİ</t>
-        </is>
-      </c>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Tedarikçinin ticari unvanı</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Tedarikçinin ticari unvanı</t>
+          <t>Adresi</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -926,7 +913,7 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Adresi</t>
+          <t>Vergi dairesi ve numarası</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
@@ -939,7 +926,7 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Vergi dairesi ve numarası</t>
+          <t>Telefon / e-posta</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -952,7 +939,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Telefon / e-posta</t>
+          <t>Proforma numarası ve tarihi</t>
         </is>
       </c>
       <c r="B28" s="7" t="n"/>
@@ -962,30 +949,30 @@
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Proforma numarası ve tarihi</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>TESLİM VE ÖDEME ŞARTLARI</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>TESLİM VE ÖDEME ŞARTLARI</t>
-        </is>
-      </c>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Para birimi</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Para birimi</t>
+          <t>Fiyatlara KDV dâhil mi</t>
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
@@ -998,7 +985,7 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Fiyatlara KDV dâhil mi</t>
+          <t>Teslim yeri</t>
         </is>
       </c>
       <c r="B33" s="7" t="n"/>
@@ -1011,7 +998,7 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Teslim yeri</t>
+          <t>Teslim süresi</t>
         </is>
       </c>
       <c r="B34" s="7" t="n"/>
@@ -1024,7 +1011,7 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Teslim süresi</t>
+          <t>Ödeme şekli</t>
         </is>
       </c>
       <c r="B35" s="7" t="n"/>
@@ -1037,7 +1024,7 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Ödeme şekli</t>
+          <t>Fiyat geçerlilik süresi</t>
         </is>
       </c>
       <c r="B36" s="7" t="n"/>
@@ -1047,21 +1034,8 @@
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Fiyat geçerlilik süresi</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Proforma, tedarikçinin kendi antetli kâğıdında, kaşe ve imzasıyla düzenlenmelidir.</t>
         </is>
@@ -1070,16 +1044,14 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="B34:G34"/>
     <mergeCell ref="B28:G28"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B36:G36"/>
     <mergeCell ref="B32:G32"/>
@@ -1088,7 +1060,9 @@
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B31:G31"/>
     <mergeCell ref="B27:G27"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
